--- a/sitepreview/trust/all-profiles.xlsx
+++ b/sitepreview/trust/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-05-19T11:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -436,14 +436,14 @@
     <t>HCert.-6</t>
   </si>
   <si>
-    <t xml:space="preserve">http://smart.who.int/trust-phw/StructureDefinition/DVC
+    <t xml:space="preserve">http://smart.who.int/trust-phw/StructureDefinition/DVCMin
 </t>
   </si>
   <si>
-    <t>DVC</t>
-  </si>
-  <si>
-    <t>Digital Vaccination Certificate (Proposed)</t>
+    <t>DVCMin</t>
+  </si>
+  <si>
+    <t>Minimal Digital Vaccination Certificate Payload (Proposed)</t>
   </si>
   <si>
     <t>SchemeInformation</t>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F6" s="2"/>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>79</v>
@@ -2293,7 +2293,7 @@
         <v>91</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>79</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>79</v>
@@ -2396,7 +2396,7 @@
         <v>95</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>79</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>79</v>
@@ -2499,7 +2499,7 @@
         <v>99</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>79</v>
@@ -3251,7 +3251,7 @@
         <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>73</v>
@@ -3326,7 +3326,7 @@
         <v>74</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>73</v>
@@ -3354,7 +3354,7 @@
         <v>74</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>73</v>
@@ -3429,7 +3429,7 @@
         <v>74</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>73</v>
@@ -3457,7 +3457,7 @@
         <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>73</v>
@@ -3532,7 +3532,7 @@
         <v>74</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>73</v>
@@ -3560,7 +3560,7 @@
         <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>73</v>
@@ -3635,7 +3635,7 @@
         <v>74</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>73</v>
